--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/103.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/103.xlsx
@@ -426,13 +426,13 @@
         <v>-2.208812298346318</v>
       </c>
       <c r="E2">
-        <v>-2.752721043276174</v>
+        <v>-3.92805930112297</v>
       </c>
       <c r="F2">
-        <v>-4.78644865144893</v>
+        <v>-3.900833605809353</v>
       </c>
       <c r="G2">
-        <v>-1.552110700209159</v>
+        <v>-3.642846008989406</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-2.018921744304698</v>
       </c>
       <c r="E3">
-        <v>-4.815169245329562</v>
+        <v>-4.634523888689584</v>
       </c>
       <c r="F3">
-        <v>-4.125467792998315</v>
+        <v>-3.89491160724674</v>
       </c>
       <c r="G3">
-        <v>-1.401788758907472</v>
+        <v>-3.174284635543119</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-1.810988707118244</v>
       </c>
       <c r="E4">
-        <v>-4.264090186388141</v>
+        <v>-5.313219873641163</v>
       </c>
       <c r="F4">
-        <v>-4.106040920667861</v>
+        <v>-3.822580222369092</v>
       </c>
       <c r="G4">
-        <v>-1.640737314840988</v>
+        <v>-3.035254965075886</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-1.598843003701708</v>
       </c>
       <c r="E5">
-        <v>-6.11957354086897</v>
+        <v>-5.747147310004152</v>
       </c>
       <c r="F5">
-        <v>-3.964007389049052</v>
+        <v>-3.893649175324873</v>
       </c>
       <c r="G5">
-        <v>-1.191231441518746</v>
+        <v>-2.253224655607089</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-1.374844562247965</v>
       </c>
       <c r="E6">
-        <v>-6.017456451996003</v>
+        <v>-7.355366926718164</v>
       </c>
       <c r="F6">
-        <v>-4.430351729068284</v>
+        <v>-3.689618970545744</v>
       </c>
       <c r="G6">
-        <v>-2.056372996750946</v>
+        <v>-2.259743119773914</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-1.137513617090422</v>
       </c>
       <c r="E7">
-        <v>-6.96442829410999</v>
+        <v>-7.205297826577977</v>
       </c>
       <c r="F7">
-        <v>-3.839802809040697</v>
+        <v>-3.242958296751834</v>
       </c>
       <c r="G7">
-        <v>-0.9895728705395808</v>
+        <v>-2.676855304994387</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-0.8829484411751878</v>
       </c>
       <c r="E8">
-        <v>-7.613911093238088</v>
+        <v>-8.569260612266266</v>
       </c>
       <c r="F8">
-        <v>-3.88311731216568</v>
+        <v>-3.423992194061846</v>
       </c>
       <c r="G8">
-        <v>-0.7619000327128227</v>
+        <v>-2.153683172332283</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-0.6061034049625336</v>
       </c>
       <c r="E9">
-        <v>-9.292494139083283</v>
+        <v>-9.771493477244615</v>
       </c>
       <c r="F9">
-        <v>-4.146240762358318</v>
+        <v>-3.530030676926808</v>
       </c>
       <c r="G9">
-        <v>0.4785746230342481</v>
+        <v>-2.214981233537428</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-0.3027674432912963</v>
       </c>
       <c r="E10">
-        <v>-10.68582407871131</v>
+        <v>-10.88292590989517</v>
       </c>
       <c r="F10">
-        <v>-3.878652411864591</v>
+        <v>-3.311170210535359</v>
       </c>
       <c r="G10">
-        <v>-0.9411561420277397</v>
+        <v>-2.114095668773678</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>0.02356789885116449</v>
       </c>
       <c r="E11">
-        <v>-11.80994529553136</v>
+        <v>-11.6115981339954</v>
       </c>
       <c r="F11">
-        <v>-3.997219951696895</v>
+        <v>-2.931877344141521</v>
       </c>
       <c r="G11">
-        <v>0.2784256608209907</v>
+        <v>-1.705127425579812</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>0.3671953829759759</v>
       </c>
       <c r="E12">
-        <v>-12.03116577928006</v>
+        <v>-11.13127195294982</v>
       </c>
       <c r="F12">
-        <v>-3.873846224193548</v>
+        <v>-3.131222302890416</v>
       </c>
       <c r="G12">
-        <v>-0.01262426080957495</v>
+        <v>-1.5199454397496</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>0.7156525320527904</v>
       </c>
       <c r="E13">
-        <v>-12.68360567193517</v>
+        <v>-13.14988905508296</v>
       </c>
       <c r="F13">
-        <v>-3.40792020971273</v>
+        <v>-2.921762149785936</v>
       </c>
       <c r="G13">
-        <v>0.4787235975835153</v>
+        <v>-1.559854066225514</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>1.0508887421778</v>
       </c>
       <c r="E14">
-        <v>-13.58315986271484</v>
+        <v>-13.55071334644988</v>
       </c>
       <c r="F14">
-        <v>-3.594171993292976</v>
+        <v>-2.578548825621031</v>
       </c>
       <c r="G14">
-        <v>0.3959765118294321</v>
+        <v>-0.8112668877944347</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>1.355265715161169</v>
       </c>
       <c r="E15">
-        <v>-15.47670956970414</v>
+        <v>-13.99730692461232</v>
       </c>
       <c r="F15">
-        <v>-3.17638323695624</v>
+        <v>-2.462328879008261</v>
       </c>
       <c r="G15">
-        <v>0.4836198944360974</v>
+        <v>-0.6922792600219496</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>1.610727451304007</v>
       </c>
       <c r="E16">
-        <v>-14.74724939112658</v>
+        <v>-15.55546426117154</v>
       </c>
       <c r="F16">
-        <v>-3.197930729837861</v>
+        <v>-2.247969761083624</v>
       </c>
       <c r="G16">
-        <v>1.650961288675129</v>
+        <v>-0.7148969071462504</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>1.802371055002722</v>
       </c>
       <c r="E17">
-        <v>-15.88999622154017</v>
+        <v>-15.78111359249975</v>
       </c>
       <c r="F17">
-        <v>-3.068747661738681</v>
+        <v>-1.982186423160597</v>
       </c>
       <c r="G17">
-        <v>1.506386454429617</v>
+        <v>-0.3081003818261462</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>1.921831661203938</v>
       </c>
       <c r="E18">
-        <v>-16.33913027362092</v>
+        <v>-17.26926072090038</v>
       </c>
       <c r="F18">
-        <v>-2.710246817155111</v>
+        <v>-1.780419318125916</v>
       </c>
       <c r="G18">
-        <v>1.351532376284667</v>
+        <v>-0.2480040486517563</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>1.966711282525298</v>
       </c>
       <c r="E19">
-        <v>-17.52978835903566</v>
+        <v>-17.63553275558877</v>
       </c>
       <c r="F19">
-        <v>-1.835217478555909</v>
+        <v>-1.208251042399047</v>
       </c>
       <c r="G19">
-        <v>1.662789867886944</v>
+        <v>-0.06748000039529851</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>1.941261710488724</v>
       </c>
       <c r="E20">
-        <v>-18.5406116846578</v>
+        <v>-19.15138961644234</v>
       </c>
       <c r="F20">
-        <v>-1.491189040866649</v>
+        <v>-0.8362627197630954</v>
       </c>
       <c r="G20">
-        <v>0.8795545198418528</v>
+        <v>-0.2628220504855342</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>1.854765463562513</v>
       </c>
       <c r="E21">
-        <v>-19.60250714013845</v>
+        <v>-19.235614704511</v>
       </c>
       <c r="F21">
-        <v>-1.055162947789879</v>
+        <v>-0.3669271450523544</v>
       </c>
       <c r="G21">
-        <v>1.632372575472121</v>
+        <v>-0.6690590936095016</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>1.71861284641569</v>
       </c>
       <c r="E22">
-        <v>-21.02827453908342</v>
+        <v>-19.38338333985529</v>
       </c>
       <c r="F22">
-        <v>-0.6696581542424477</v>
+        <v>-0.40105174021068</v>
       </c>
       <c r="G22">
-        <v>0.6636804663170573</v>
+        <v>-0.4474313119374527</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>1.544329916467421</v>
       </c>
       <c r="E23">
-        <v>-20.28515648289872</v>
+        <v>-19.65479742950502</v>
       </c>
       <c r="F23">
-        <v>-0.6401152591890061</v>
+        <v>0.09360702600364199</v>
       </c>
       <c r="G23">
-        <v>0.7798773041999367</v>
+        <v>-0.2266344771957608</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>1.342184067343703</v>
       </c>
       <c r="E24">
-        <v>-21.0916686467168</v>
+        <v>-21.17386950690403</v>
       </c>
       <c r="F24">
-        <v>-0.3145229664164521</v>
+        <v>0.389402114930095</v>
       </c>
       <c r="G24">
-        <v>1.096385321027498</v>
+        <v>-0.1660150778261661</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>1.121759204061174</v>
       </c>
       <c r="E25">
-        <v>-20.46577466869466</v>
+        <v>-21.09395552609067</v>
       </c>
       <c r="F25">
-        <v>0.02010515798583905</v>
+        <v>0.6778603537699529</v>
       </c>
       <c r="G25">
-        <v>1.227386918561998</v>
+        <v>-0.7689779790757845</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>0.8907409559034494</v>
       </c>
       <c r="E26">
-        <v>-21.05552236718757</v>
+        <v>-21.69304999493542</v>
       </c>
       <c r="F26">
-        <v>0.1832454910279793</v>
+        <v>0.8821407255047278</v>
       </c>
       <c r="G26">
-        <v>1.595652004350525</v>
+        <v>-1.109500693245219</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>0.6549143007479141</v>
       </c>
       <c r="E27">
-        <v>-21.47043474119235</v>
+        <v>-21.32350840201349</v>
       </c>
       <c r="F27">
-        <v>0.1800214850962836</v>
+        <v>1.385402087197123</v>
       </c>
       <c r="G27">
-        <v>1.726544353882229</v>
+        <v>-0.7466549705044789</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>0.4205073438367363</v>
       </c>
       <c r="E28">
-        <v>-21.52145705783678</v>
+        <v>-21.11917006936538</v>
       </c>
       <c r="F28">
-        <v>0.6108023557785273</v>
+        <v>1.164507978831801</v>
       </c>
       <c r="G28">
-        <v>0.4355507732058798</v>
+        <v>-0.9224482491853182</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>0.1911515704284619</v>
       </c>
       <c r="E29">
-        <v>-20.10977774152967</v>
+        <v>-20.32278810190246</v>
       </c>
       <c r="F29">
-        <v>0.7697163583315845</v>
+        <v>1.309566708205633</v>
       </c>
       <c r="G29">
-        <v>-0.9370179601036507</v>
+        <v>-1.496490224603863</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-0.03113348379196615</v>
       </c>
       <c r="E30">
-        <v>-20.56590828595226</v>
+        <v>-20.66756347047644</v>
       </c>
       <c r="F30">
-        <v>0.7028082948400656</v>
+        <v>1.20470533542005</v>
       </c>
       <c r="G30">
-        <v>-0.016226134356302</v>
+        <v>-2.028230049121602</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-0.2424115349483517</v>
       </c>
       <c r="E31">
-        <v>-20.85239313709951</v>
+        <v>-20.36859361649005</v>
       </c>
       <c r="F31">
-        <v>0.8980304690252279</v>
+        <v>0.8742430706864373</v>
       </c>
       <c r="G31">
-        <v>-0.8850357740460145</v>
+        <v>-2.217129777592416</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-0.4397957803051154</v>
       </c>
       <c r="E32">
-        <v>-19.07618524859696</v>
+        <v>-20.13982869504457</v>
       </c>
       <c r="F32">
-        <v>0.4886347312136562</v>
+        <v>0.9149854930257282</v>
       </c>
       <c r="G32">
-        <v>-0.7260799299779085</v>
+        <v>-2.300946169555683</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-0.6196389601628172</v>
       </c>
       <c r="E33">
-        <v>-19.33786311913019</v>
+        <v>-19.55232711965945</v>
       </c>
       <c r="F33">
-        <v>0.7040152261459445</v>
+        <v>0.9339219718537248</v>
       </c>
       <c r="G33">
-        <v>-0.5017043955082645</v>
+        <v>-2.208780581742373</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-0.7752048663376362</v>
       </c>
       <c r="E34">
-        <v>-18.66284878354685</v>
+        <v>-19.1998941015385</v>
       </c>
       <c r="F34">
-        <v>0.3391127582735399</v>
+        <v>0.820785208714174</v>
       </c>
       <c r="G34">
-        <v>-1.349647666663951</v>
+        <v>-2.675458254776815</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-0.9007928542129758</v>
       </c>
       <c r="E35">
-        <v>-19.17904500720718</v>
+        <v>-18.63364918314539</v>
       </c>
       <c r="F35">
-        <v>0.4546998321905717</v>
+        <v>0.9774924405061732</v>
       </c>
       <c r="G35">
-        <v>-1.959761346278395</v>
+        <v>-2.433440823128395</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-0.9912879684010842</v>
       </c>
       <c r="E36">
-        <v>-17.59316888124702</v>
+        <v>-18.79814600147402</v>
       </c>
       <c r="F36">
-        <v>0.2523843479352372</v>
+        <v>0.6882803873297678</v>
       </c>
       <c r="G36">
-        <v>-1.438065716926806</v>
+        <v>-3.306832257844459</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-1.041335118092769</v>
       </c>
       <c r="E37">
-        <v>-16.83175579007133</v>
+        <v>-17.59005329112974</v>
       </c>
       <c r="F37">
-        <v>-0.1494649628368309</v>
+        <v>0.7930663786816969</v>
       </c>
       <c r="G37">
-        <v>-1.329933367977591</v>
+        <v>-3.038092102603041</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-1.04835071902881</v>
       </c>
       <c r="E38">
-        <v>-16.89064859454108</v>
+        <v>-16.49611435357082</v>
       </c>
       <c r="F38">
-        <v>-0.526276868859284</v>
+        <v>0.7703790522538241</v>
       </c>
       <c r="G38">
-        <v>-0.8979435911036329</v>
+        <v>-2.807462947609714</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-1.012492579996255</v>
       </c>
       <c r="E39">
-        <v>-15.64489709434902</v>
+        <v>-16.50505356126196</v>
       </c>
       <c r="F39">
-        <v>-0.1062639460460311</v>
+        <v>0.7209934444337232</v>
       </c>
       <c r="G39">
-        <v>-2.032613211415597</v>
+        <v>-2.156798395684737</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-0.9363611592491284</v>
       </c>
       <c r="E40">
-        <v>-14.31927689808368</v>
+        <v>-15.68078977933382</v>
       </c>
       <c r="F40">
-        <v>-0.3689591302914216</v>
+        <v>0.3387275674312381</v>
       </c>
       <c r="G40">
-        <v>-0.8549925732771285</v>
+        <v>-2.32362671704523</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-0.825760883235465</v>
       </c>
       <c r="E41">
-        <v>-13.54955405710392</v>
+        <v>-15.2597775508407</v>
       </c>
       <c r="F41">
-        <v>-0.5548398052752138</v>
+        <v>0.3280623371201944</v>
       </c>
       <c r="G41">
-        <v>-1.220099398621191</v>
+        <v>-1.855730763252337</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-0.6884143044640618</v>
       </c>
       <c r="E42">
-        <v>-13.67608414935223</v>
+        <v>-14.68642292825555</v>
       </c>
       <c r="F42">
-        <v>-0.6890957953491381</v>
+        <v>-0.00378992811531549</v>
       </c>
       <c r="G42">
-        <v>-0.5377396837032313</v>
+        <v>-2.497076129484266</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-0.5318579249231989</v>
       </c>
       <c r="E43">
-        <v>-13.58541051429665</v>
+        <v>-14.04656313639375</v>
       </c>
       <c r="F43">
-        <v>-0.8177536785149433</v>
+        <v>-0.1763595673035225</v>
       </c>
       <c r="G43">
-        <v>-1.0202848015074</v>
+        <v>-2.039174712674432</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-0.3631446549980192</v>
       </c>
       <c r="E44">
-        <v>-13.17312465521632</v>
+        <v>-13.20623685716041</v>
       </c>
       <c r="F44">
-        <v>-0.4843788739930879</v>
+        <v>0.129428117602901</v>
       </c>
       <c r="G44">
-        <v>-0.3182505144495517</v>
+        <v>-1.824621566819806</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-0.1897220932116285</v>
       </c>
       <c r="E45">
-        <v>-11.03835219478643</v>
+        <v>-12.03769583879912</v>
       </c>
       <c r="F45">
-        <v>-1.035198465015008</v>
+        <v>-0.1614870589536602</v>
       </c>
       <c r="G45">
-        <v>0.06118104144293689</v>
+        <v>-1.237486383793443</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-0.01831923974849549</v>
       </c>
       <c r="E46">
-        <v>-10.92164436266075</v>
+        <v>-11.23948889631111</v>
       </c>
       <c r="F46">
-        <v>-0.8047955272329507</v>
+        <v>-0.5218061699863751</v>
       </c>
       <c r="G46">
-        <v>0.2008264733804741</v>
+        <v>-1.350041621583124</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>0.1453816691506248</v>
       </c>
       <c r="E47">
-        <v>-10.39287709515512</v>
+        <v>-10.70734338719576</v>
       </c>
       <c r="F47">
-        <v>-0.9481826111879339</v>
+        <v>-0.4292079482318352</v>
       </c>
       <c r="G47">
-        <v>0.3389358121877895</v>
+        <v>-1.968766030145213</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>0.2956739828465837</v>
       </c>
       <c r="E48">
-        <v>-10.50006154644267</v>
+        <v>-9.714679242344383</v>
       </c>
       <c r="F48">
-        <v>-1.078977682252962</v>
+        <v>-0.6522947451123673</v>
       </c>
       <c r="G48">
-        <v>0.4080500714111541</v>
+        <v>-1.569530790836804</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>0.4283591593574892</v>
       </c>
       <c r="E49">
-        <v>-8.612992085758338</v>
+        <v>-10.21767949274637</v>
       </c>
       <c r="F49">
-        <v>-1.260192163656785</v>
+        <v>-0.6115531511404791</v>
       </c>
       <c r="G49">
-        <v>0.5709256013977572</v>
+        <v>-1.258011766136924</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>0.5409173575578986</v>
       </c>
       <c r="E50">
-        <v>-8.558437559387933</v>
+        <v>-9.23789885644681</v>
       </c>
       <c r="F50">
-        <v>-1.24684882153249</v>
+        <v>-0.7338897626555213</v>
       </c>
       <c r="G50">
-        <v>-0.7178697770405159</v>
+        <v>-1.212577839155967</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>0.6310241529791826</v>
       </c>
       <c r="E51">
-        <v>-8.318174842436974</v>
+        <v>-8.831712851854808</v>
       </c>
       <c r="F51">
-        <v>-1.350156177070422</v>
+        <v>-0.8074015710821579</v>
       </c>
       <c r="G51">
-        <v>0.2895722676517168</v>
+        <v>-1.038277616513338</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>0.6976452977130093</v>
       </c>
       <c r="E52">
-        <v>-7.107170323305768</v>
+        <v>-7.851402384096352</v>
       </c>
       <c r="F52">
-        <v>-1.570655154184608</v>
+        <v>-1.00552634464673</v>
       </c>
       <c r="G52">
-        <v>0.4386262700118627</v>
+        <v>-0.9633003811399247</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>0.7405792334997789</v>
       </c>
       <c r="E53">
-        <v>-6.611316004887887</v>
+        <v>-6.930953814245291</v>
       </c>
       <c r="F53">
-        <v>-1.100124245311628</v>
+        <v>-0.9338684224675584</v>
       </c>
       <c r="G53">
-        <v>-0.03955223822600679</v>
+        <v>-1.798130581414558</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>0.7588197941015448</v>
       </c>
       <c r="E54">
-        <v>-5.290428063960558</v>
+        <v>-7.07375018512916</v>
       </c>
       <c r="F54">
-        <v>-1.55498492802585</v>
+        <v>-1.036522196124682</v>
       </c>
       <c r="G54">
-        <v>-0.2683307982628814</v>
+        <v>-1.575314313893911</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>0.7509961870482472</v>
       </c>
       <c r="E55">
-        <v>-4.817279514217137</v>
+        <v>-6.145643965731129</v>
       </c>
       <c r="F55">
-        <v>-1.321643771066063</v>
+        <v>-0.939786279193158</v>
       </c>
       <c r="G55">
-        <v>0.3434447752122768</v>
+        <v>-1.585315471968049</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>0.7160470733315291</v>
       </c>
       <c r="E56">
-        <v>-6.383225826069546</v>
+        <v>-5.768662090014594</v>
       </c>
       <c r="F56">
-        <v>-1.514538232849359</v>
+        <v>-1.11146956526037</v>
       </c>
       <c r="G56">
-        <v>0.2207625786179652</v>
+        <v>-1.912738357438587</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>0.653667594309545</v>
       </c>
       <c r="E57">
-        <v>-4.371804469134588</v>
+        <v>-4.991920114322943</v>
       </c>
       <c r="F57">
-        <v>-1.630463280666733</v>
+        <v>-1.013555709882065</v>
       </c>
       <c r="G57">
-        <v>-0.5758275101325464</v>
+        <v>-2.847841671552205</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>0.5647501865429043</v>
       </c>
       <c r="E58">
-        <v>-4.103551254342219</v>
+        <v>-5.110606889589977</v>
       </c>
       <c r="F58">
-        <v>-1.944787291659005</v>
+        <v>-0.977107544158887</v>
       </c>
       <c r="G58">
-        <v>-0.4525163098857732</v>
+        <v>-2.246494316525751</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>0.452151630211136</v>
       </c>
       <c r="E59">
-        <v>-4.173692788247025</v>
+        <v>-4.501749030784689</v>
       </c>
       <c r="F59">
-        <v>-1.377990150171888</v>
+        <v>-1.295826872590414</v>
       </c>
       <c r="G59">
-        <v>-0.7723911515267731</v>
+        <v>-2.37482099326452</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>0.3202428975641</v>
       </c>
       <c r="E60">
-        <v>-3.847316609566207</v>
+        <v>-3.844341402143168</v>
       </c>
       <c r="F60">
-        <v>-1.998690815293974</v>
+        <v>-1.099285937499994</v>
       </c>
       <c r="G60">
-        <v>-1.08133126125156</v>
+        <v>-2.311109544361246</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>0.1737535865721897</v>
       </c>
       <c r="E61">
-        <v>-3.843893083216408</v>
+        <v>-3.500308703306443</v>
       </c>
       <c r="F61">
-        <v>-1.87276737292481</v>
+        <v>-1.208835869785424</v>
       </c>
       <c r="G61">
-        <v>-1.344645432354112</v>
+        <v>-3.003970309729774</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>0.01829050740004577</v>
       </c>
       <c r="E62">
-        <v>-2.827504263038843</v>
+        <v>-3.758078500771055</v>
       </c>
       <c r="F62">
-        <v>-2.096761232111408</v>
+        <v>-1.125099522506033</v>
       </c>
       <c r="G62">
-        <v>-1.113807712991811</v>
+        <v>-2.674355843112238</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-0.1396150252999308</v>
       </c>
       <c r="E63">
-        <v>-3.021848253552024</v>
+        <v>-3.230891670694103</v>
       </c>
       <c r="F63">
-        <v>-1.856714441025959</v>
+        <v>-1.270842483354578</v>
       </c>
       <c r="G63">
-        <v>-1.441667590473533</v>
+        <v>-3.009200971681822</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-0.2935114816764696</v>
       </c>
       <c r="E64">
-        <v>-3.091179190609457</v>
+        <v>-3.347676486877914</v>
       </c>
       <c r="F64">
-        <v>-1.739119404524541</v>
+        <v>-1.436453007991866</v>
       </c>
       <c r="G64">
-        <v>-1.946502611393614</v>
+        <v>-3.443571030798516</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-0.436259312313092</v>
       </c>
       <c r="E65">
-        <v>-2.024678277063011</v>
+        <v>-3.371328706619976</v>
       </c>
       <c r="F65">
-        <v>-2.359632858613595</v>
+        <v>-1.652596429302133</v>
       </c>
       <c r="G65">
-        <v>-2.191867004582237</v>
+        <v>-3.094540214593155</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-0.5601578713744726</v>
       </c>
       <c r="E66">
-        <v>-1.804304617953741</v>
+        <v>-2.961637663146039</v>
       </c>
       <c r="F66">
-        <v>-2.358629705688804</v>
+        <v>-1.517739872861179</v>
       </c>
       <c r="G66">
-        <v>-1.62791888251293</v>
+        <v>-3.137656759696622</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-0.6589389106642795</v>
       </c>
       <c r="E67">
-        <v>-1.136313945556294</v>
+        <v>-2.826041565934365</v>
       </c>
       <c r="F67">
-        <v>-2.083039326084034</v>
+        <v>-1.723104577526218</v>
       </c>
       <c r="G67">
-        <v>-1.195055121616604</v>
+        <v>-3.345542466835157</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-0.7277043948665001</v>
       </c>
       <c r="E68">
-        <v>-1.274246735355925</v>
+        <v>-3.407778393907715</v>
       </c>
       <c r="F68">
-        <v>-2.542742644635023</v>
+        <v>-1.645054144099643</v>
       </c>
       <c r="G68">
-        <v>-1.412177250809705</v>
+        <v>-2.757232040142353</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-0.7624804995735772</v>
       </c>
       <c r="E69">
-        <v>-1.610132709452851</v>
+        <v>-2.527370591232474</v>
       </c>
       <c r="F69">
-        <v>-2.12446680826544</v>
+        <v>-1.708422593679</v>
       </c>
       <c r="G69">
-        <v>-2.535110987184952</v>
+        <v>-2.676355412617958</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-0.7615393414881266</v>
       </c>
       <c r="E70">
-        <v>-2.579674466021067</v>
+        <v>-2.533379876240653</v>
       </c>
       <c r="F70">
-        <v>-2.654588811361012</v>
+        <v>-2.041418834297776</v>
       </c>
       <c r="G70">
-        <v>-2.25503883456261</v>
+        <v>-3.602646054506036</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-0.7253682382993034</v>
       </c>
       <c r="E71">
-        <v>-1.316723821547873</v>
+        <v>-2.385393874143993</v>
       </c>
       <c r="F71">
-        <v>-2.971373901907002</v>
+        <v>-1.982496232569244</v>
       </c>
       <c r="G71">
-        <v>-1.859190283340876</v>
+        <v>-3.07480274208802</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-0.6548592988654317</v>
       </c>
       <c r="E72">
-        <v>-2.466118451804725</v>
+        <v>-3.100548603331327</v>
       </c>
       <c r="F72">
-        <v>-2.897001419748856</v>
+        <v>-2.10664779706382</v>
       </c>
       <c r="G72">
-        <v>-1.020519850240688</v>
+        <v>-2.32317317230635</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-0.5526716954866588</v>
       </c>
       <c r="E73">
-        <v>-2.432856810218386</v>
+        <v>-3.316194535576589</v>
       </c>
       <c r="F73">
-        <v>-2.953303067014931</v>
+        <v>-2.081887895394143</v>
       </c>
       <c r="G73">
-        <v>-1.926907492346668</v>
+        <v>-2.842409066322261</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-0.4231526690922172</v>
       </c>
       <c r="E74">
-        <v>-1.955845472146422</v>
+        <v>-3.647262213329354</v>
       </c>
       <c r="F74">
-        <v>-2.833396057092299</v>
+        <v>-1.88932560893937</v>
       </c>
       <c r="G74">
-        <v>-1.356017156281508</v>
+        <v>-2.362452795129803</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-0.2690445196491898</v>
       </c>
       <c r="E75">
-        <v>-2.947875630636728</v>
+        <v>-4.510538798833577</v>
       </c>
       <c r="F75">
-        <v>-3.083079246174515</v>
+        <v>-2.461646304268354</v>
       </c>
       <c r="G75">
-        <v>-0.7111758539601096</v>
+        <v>-1.388592924387937</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-0.09358624338362552</v>
       </c>
       <c r="E76">
-        <v>-3.593273746209908</v>
+        <v>-4.154084495793812</v>
       </c>
       <c r="F76">
-        <v>-2.948713911603421</v>
+        <v>-2.258954741212148</v>
       </c>
       <c r="G76">
-        <v>-0.185447980141688</v>
+        <v>-2.116853353207891</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>0.09927745625048207</v>
       </c>
       <c r="E77">
-        <v>-3.394722803343601</v>
+        <v>-4.08092246972589</v>
       </c>
       <c r="F77">
-        <v>-3.088525761847922</v>
+        <v>-2.662967747640329</v>
       </c>
       <c r="G77">
-        <v>-0.07411764420153726</v>
+        <v>-1.387285258899925</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>0.3090860920240249</v>
       </c>
       <c r="E78">
-        <v>-4.573366847215996</v>
+        <v>-5.324817295574807</v>
       </c>
       <c r="F78">
-        <v>-3.184367041984422</v>
+        <v>-2.479425553834639</v>
       </c>
       <c r="G78">
-        <v>0.8406953363018876</v>
+        <v>-1.012412324215013</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>0.5347750868418758</v>
       </c>
       <c r="E79">
-        <v>-5.361570390621059</v>
+        <v>-6.629094793842</v>
       </c>
       <c r="F79">
-        <v>-3.258332795747792</v>
+        <v>-2.683425109019865</v>
       </c>
       <c r="G79">
-        <v>0.2660409099585772</v>
+        <v>-0.8898559283511933</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>0.7740755932067999</v>
       </c>
       <c r="E80">
-        <v>-4.208457883203911</v>
+        <v>-6.064511825409706</v>
       </c>
       <c r="F80">
-        <v>-3.750108015032969</v>
+        <v>-2.686193512880021</v>
       </c>
       <c r="G80">
-        <v>0.70100686727234</v>
+        <v>-0.7163005784549014</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>1.026866275203049</v>
       </c>
       <c r="E81">
-        <v>-6.832762912336975</v>
+        <v>-7.132955454305443</v>
       </c>
       <c r="F81">
-        <v>-3.159894583803516</v>
+        <v>-2.674054616959397</v>
       </c>
       <c r="G81">
-        <v>0.8261785941121835</v>
+        <v>-0.7798431895356726</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>1.289723561473692</v>
       </c>
       <c r="E82">
-        <v>-8.548461331149035</v>
+        <v>-7.465916034193413</v>
       </c>
       <c r="F82">
-        <v>-3.608738834071206</v>
+        <v>-2.785882559602525</v>
       </c>
       <c r="G82">
-        <v>1.482365135996665</v>
+        <v>-0.39643235790498</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>1.556753966193243</v>
       </c>
       <c r="E83">
-        <v>-8.737556820287326</v>
+        <v>-9.15283600068673</v>
       </c>
       <c r="F83">
-        <v>-3.408835555692823</v>
+        <v>-2.938968169109485</v>
       </c>
       <c r="G83">
-        <v>1.702976580188157</v>
+        <v>0.4622172175247092</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>1.822239982685885</v>
       </c>
       <c r="E84">
-        <v>-9.33860758990339</v>
+        <v>-10.31292235807569</v>
       </c>
       <c r="F84">
-        <v>-3.702135602002044</v>
+        <v>-3.088558068176631</v>
       </c>
       <c r="G84">
-        <v>1.48302393455898</v>
+        <v>-0.3844117670518863</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>2.076173853052989</v>
       </c>
       <c r="E85">
-        <v>-10.26587604161</v>
+        <v>-11.38057803249409</v>
       </c>
       <c r="F85">
-        <v>-3.833703539853884</v>
+        <v>-2.925083903071163</v>
       </c>
       <c r="G85">
-        <v>1.796893446591742</v>
+        <v>0.4910917957182325</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>2.307633741837939</v>
       </c>
       <c r="E86">
-        <v>-13.14177855813523</v>
+        <v>-12.28060771304457</v>
       </c>
       <c r="F86">
-        <v>-3.231211218612734</v>
+        <v>-2.799501748071952</v>
       </c>
       <c r="G86">
-        <v>2.180499600409251</v>
+        <v>0.8844971643319848</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>2.506312332348112</v>
       </c>
       <c r="E87">
-        <v>-14.40089358512392</v>
+        <v>-13.65142660838047</v>
       </c>
       <c r="F87">
-        <v>-3.609498446979573</v>
+        <v>-3.048065812792986</v>
       </c>
       <c r="G87">
-        <v>2.749277808420355</v>
+        <v>0.3383399139907207</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>2.660414092118776</v>
       </c>
       <c r="E88">
-        <v>-14.59302768032136</v>
+        <v>-16.05027250209365</v>
       </c>
       <c r="F88">
-        <v>-3.959226052400093</v>
+        <v>-3.024705852034039</v>
       </c>
       <c r="G88">
-        <v>1.580254657047375</v>
+        <v>0.6568210159596874</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>2.76095145554631</v>
       </c>
       <c r="E89">
-        <v>-16.09112839459085</v>
+        <v>-17.02463255500603</v>
       </c>
       <c r="F89">
-        <v>-3.556474649526376</v>
+        <v>-3.116778060487801</v>
       </c>
       <c r="G89">
-        <v>3.038920748196731</v>
+        <v>0.4974778380634866</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>2.800765552901808</v>
       </c>
       <c r="E90">
-        <v>-18.16053233272002</v>
+        <v>-18.32669562948347</v>
       </c>
       <c r="F90">
-        <v>-3.388306954716646</v>
+        <v>-3.214807887302498</v>
       </c>
       <c r="G90">
-        <v>2.736552071367397</v>
+        <v>1.193232020233337</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>2.774088000380524</v>
       </c>
       <c r="E91">
-        <v>-20.22108310416419</v>
+        <v>-20.3339100340653</v>
       </c>
       <c r="F91">
-        <v>-4.084172021233954</v>
+        <v>-3.127003427707959</v>
       </c>
       <c r="G91">
-        <v>2.412853549628539</v>
+        <v>0.663091189211067</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>2.680708929457311</v>
       </c>
       <c r="E92">
-        <v>-22.54030936787451</v>
+        <v>-22.80047019961518</v>
       </c>
       <c r="F92">
-        <v>-3.975200289395679</v>
+        <v>-3.279430485129693</v>
       </c>
       <c r="G92">
-        <v>2.650170006611194</v>
+        <v>0.473042701438126</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>2.523979097827393</v>
       </c>
       <c r="E93">
-        <v>-23.70429926985809</v>
+        <v>-23.90715226303168</v>
       </c>
       <c r="F93">
-        <v>-3.818030000225515</v>
+        <v>-3.055478872680638</v>
       </c>
       <c r="G93">
-        <v>1.062207248880062</v>
+        <v>0.1832838925678761</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>2.311573026308499</v>
       </c>
       <c r="E94">
-        <v>-26.97295180859455</v>
+        <v>-27.0648436031582</v>
       </c>
       <c r="F94">
-        <v>-3.381880480405727</v>
+        <v>-3.051110062998274</v>
       </c>
       <c r="G94">
-        <v>0.8659250038566734</v>
+        <v>0.21510816683689</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>2.057780767597185</v>
       </c>
       <c r="E95">
-        <v>-29.05730876789705</v>
+        <v>-28.51439907606547</v>
       </c>
       <c r="F95">
-        <v>-3.393401414243863</v>
+        <v>-3.139650112846499</v>
       </c>
       <c r="G95">
-        <v>0.9041915997451091</v>
+        <v>-0.4632027508865406</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>1.777252812516655</v>
       </c>
       <c r="E96">
-        <v>-31.30788562988809</v>
+        <v>-30.72066255565445</v>
       </c>
       <c r="F96">
-        <v>-3.932035720770602</v>
+        <v>-3.081950181404499</v>
       </c>
       <c r="G96">
-        <v>0.442304286105993</v>
+        <v>-0.902426069763806</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>1.48760574728952</v>
       </c>
       <c r="E97">
-        <v>-33.99056042474302</v>
+        <v>-34.04068383929692</v>
       </c>
       <c r="F97">
-        <v>-4.092266827494111</v>
+        <v>-3.384806274072415</v>
       </c>
       <c r="G97">
-        <v>0.7164671149407363</v>
+        <v>-1.441233909007888</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>1.207025576465345</v>
       </c>
       <c r="E98">
-        <v>-36.44327251677744</v>
+        <v>-35.96493207158422</v>
       </c>
       <c r="F98">
-        <v>-4.321793352564006</v>
+        <v>-3.355502777198383</v>
       </c>
       <c r="G98">
-        <v>-0.8234596270155704</v>
+        <v>-1.924374925009125</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>0.9532111573182007</v>
       </c>
       <c r="E99">
-        <v>-38.06171742780077</v>
+        <v>-39.3189033248622</v>
       </c>
       <c r="F99">
-        <v>-4.504351445895169</v>
+        <v>-3.370508652700096</v>
       </c>
       <c r="G99">
-        <v>-1.090309460754064</v>
+        <v>-2.220082784213445</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>0.7378101039774653</v>
       </c>
       <c r="E100">
-        <v>-40.85796635076807</v>
+        <v>-41.67987306197523</v>
       </c>
       <c r="F100">
-        <v>-4.374675499191324</v>
+        <v>-3.534795446227711</v>
       </c>
       <c r="G100">
-        <v>-2.113920209860097</v>
+        <v>-2.92585798773067</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>0.5789869488070959</v>
       </c>
       <c r="E101">
-        <v>-43.00995380513812</v>
+        <v>-43.28186149845468</v>
       </c>
       <c r="F101">
-        <v>-4.339852590312438</v>
+        <v>-3.502404624043444</v>
       </c>
       <c r="G101">
-        <v>-2.214696526621051</v>
+        <v>-2.621420219939291</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>0.4747872211109623</v>
       </c>
       <c r="E102">
-        <v>-46.76214774146562</v>
+        <v>-46.01726584465493</v>
       </c>
       <c r="F102">
-        <v>-3.749364969472658</v>
+        <v>-3.594809836193132</v>
       </c>
       <c r="G102">
-        <v>-3.057392583096993</v>
+        <v>-3.426816359824264</v>
       </c>
     </row>
   </sheetData>
